--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>136611388</v>
       </c>
       <c r="B131" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>136611389</v>
       </c>
       <c r="B132" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>136611397</v>
       </c>
       <c r="B133" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>136611405</v>
       </c>
       <c r="B134" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>136611407</v>
       </c>
       <c r="B135" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>136611412</v>
       </c>
       <c r="B136" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>136611415</v>
       </c>
       <c r="B137" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>136611422</v>
       </c>
       <c r="B138" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>136611424</v>
       </c>
       <c r="B139" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>136611425</v>
       </c>
       <c r="B140" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>136611426</v>
       </c>
       <c r="B141" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136611430</v>
       </c>
       <c r="B142" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>136612720</v>
       </c>
       <c r="B143" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>136612756</v>
       </c>
       <c r="B144" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136612771</v>
       </c>
       <c r="B145" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>136611428</v>
       </c>
       <c r="B147" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>136612775</v>
       </c>
       <c r="B148" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>136611349</v>
       </c>
       <c r="B155" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136611386</v>
       </c>
       <c r="B156" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>136612747</v>
       </c>
       <c r="B157" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136611334</v>
       </c>
       <c r="B158" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 36371-2025 artfynd.xlsx
+++ b/artfynd/A 36371-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136611394</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136612746</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>136611383</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>136611392</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>136612749</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>136612759</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136611420</v>
       </c>
       <c r="B9" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>136612780</v>
       </c>
       <c r="B10" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>136611338</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>136611343</v>
       </c>
       <c r="B55" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>136611344</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>136611345</v>
       </c>
       <c r="B57" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>136611365</v>
       </c>
       <c r="B58" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>136611384</v>
       </c>
       <c r="B59" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>136611385</v>
       </c>
       <c r="B60" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>136611391</v>
       </c>
       <c r="B61" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>136611409</v>
       </c>
       <c r="B62" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>136611417</v>
       </c>
       <c r="B63" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>136611418</v>
       </c>
       <c r="B64" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>136611419</v>
       </c>
       <c r="B65" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136611427</v>
       </c>
       <c r="B66" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>136611432</v>
       </c>
       <c r="B67" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>136611433</v>
       </c>
       <c r="B68" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>136611434</v>
       </c>
       <c r="B69" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         <v>136612721</v>
       </c>
       <c r="B70" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>136612723</v>
       </c>
       <c r="B71" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>136612725</v>
       </c>
       <c r="B72" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>136612748</v>
       </c>
       <c r="B73" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>136612768</v>
       </c>
       <c r="B74" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>136612777</v>
       </c>
       <c r="B75" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>136612778</v>
       </c>
       <c r="B76" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>136612781</v>
       </c>
       <c r="B77" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         <v>136612782</v>
       </c>
       <c r="B78" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>136611380</v>
       </c>
       <c r="B79" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>136611413</v>
       </c>
       <c r="B80" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>136611341</v>
       </c>
       <c r="B99" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>136611356</v>
       </c>
       <c r="B100" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>136611359</v>
       </c>
       <c r="B101" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>136611393</v>
       </c>
       <c r="B102" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>136611401</v>
       </c>
       <c r="B103" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>136612736</v>
       </c>
       <c r="B104" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>136612743</v>
       </c>
       <c r="B105" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>136612766</v>
       </c>
       <c r="B106" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>136611342</v>
       </c>
       <c r="B114" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>136611350</v>
       </c>
       <c r="B115" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>136611351</v>
       </c>
       <c r="B116" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>136611358</v>
       </c>
       <c r="B117" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>136611362</v>
       </c>
       <c r="B118" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>136611364</v>
       </c>
       <c r="B119" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>136611368</v>
       </c>
       <c r="B120" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>136611387</v>
       </c>
       <c r="B121" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>136611402</v>
       </c>
       <c r="B122" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>136611438</v>
       </c>
       <c r="B123" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>136611347</v>
       </c>
       <c r="B124" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>136611388</v>
       </c>
       <c r="B131" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>136611389</v>
       </c>
       <c r="B132" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>136611397</v>
       </c>
       <c r="B133" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>136611405</v>
       </c>
       <c r="B134" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>136611407</v>
       </c>
       <c r="B135" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>136611412</v>
       </c>
       <c r="B136" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>136611415</v>
       </c>
       <c r="B137" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>136611422</v>
       </c>
       <c r="B138" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>136611424</v>
       </c>
       <c r="B139" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>136611425</v>
       </c>
       <c r="B140" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>136611426</v>
       </c>
       <c r="B141" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136611430</v>
       </c>
       <c r="B142" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>136612720</v>
       </c>
       <c r="B143" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>136612756</v>
       </c>
       <c r="B144" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>136612771</v>
       </c>
       <c r="B145" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>136611428</v>
       </c>
       <c r="B147" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>136612775</v>
       </c>
       <c r="B148" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>136611349</v>
       </c>
       <c r="B155" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136611386</v>
       </c>
       <c r="B156" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>136612747</v>
       </c>
       <c r="B157" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136611334</v>
       </c>
       <c r="B158" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>136611340</v>
       </c>
       <c r="B250" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>136611353</v>
       </c>
       <c r="B251" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>136611360</v>
       </c>
       <c r="B252" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>136611404</v>
       </c>
       <c r="B253" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>136612729</v>
       </c>
       <c r="B254" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>136612733</v>
       </c>
       <c r="B255" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30212,7 +30212,7 @@
         <v>136612737</v>
       </c>
       <c r="B256" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>136612742</v>
       </c>
       <c r="B257" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>136612755</v>
       </c>
       <c r="B258" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>136611369</v>
       </c>
       <c r="B262" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>136611373</v>
       </c>
       <c r="B263" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>136611381</v>
       </c>
       <c r="B264" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>136611403</v>
       </c>
       <c r="B265" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31382,7 +31382,7 @@
         <v>136611414</v>
       </c>
       <c r="B266" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>136611437</v>
       </c>
       <c r="B267" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31616,7 +31616,7 @@
         <v>136612731</v>
       </c>
       <c r="B268" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>136612735</v>
       </c>
       <c r="B269" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31860,7 +31860,7 @@
         <v>136612738</v>
       </c>
       <c r="B270" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
